--- a/jogos_2024-12-24.xlsx
+++ b/jogos_2024-12-24.xlsx
@@ -643,25 +643,25 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -669,83 +669,83 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>6.72</v>
+        <v>1.28</v>
       </c>
       <c r="M2" t="n">
-        <v>3.94</v>
+        <v>4.75</v>
       </c>
       <c r="N2" t="n">
-        <v>1.47</v>
+        <v>11.1</v>
       </c>
       <c r="O2" t="n">
-        <v>5.5</v>
+        <v>1.8</v>
       </c>
       <c r="P2" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.1</v>
+        <v>10</v>
       </c>
       <c r="R2" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X2" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AD2" t="n">
         <v>1.4</v>
       </c>
-      <c r="S2" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T2" t="n">
-        <v>3</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X2" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['1', '47', '53', '59', '64', '70', '82', '90']</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>['90']</t>
+          <t>['23']</t>
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.11</v>
+        <v>3.25</v>
       </c>
       <c r="AI2" t="n">
-        <v>3.4</v>
+        <v>1.2</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.4</v>
+        <v>6.5</v>
       </c>
       <c r="AK2" s="3" t="n">
         <v>45650.41666666666</v>
@@ -772,25 +772,25 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -798,83 +798,83 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.28</v>
+        <v>6.72</v>
       </c>
       <c r="M3" t="n">
-        <v>4.75</v>
+        <v>3.94</v>
       </c>
       <c r="N3" t="n">
-        <v>11.1</v>
+        <v>1.47</v>
       </c>
       <c r="O3" t="n">
-        <v>1.8</v>
+        <v>5.5</v>
       </c>
       <c r="P3" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>10</v>
+        <v>2.1</v>
       </c>
       <c r="R3" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S3" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="T3" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="U3" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V3" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="X3" t="n">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.72</v>
+        <v>3.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.75</v>
+        <v>2</v>
       </c>
       <c r="AD3" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>['90']</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AJ3" t="n">
         <v>1.4</v>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>['1', '47', '53', '59', '64', '70', '82', '90']</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>['23']</t>
-        </is>
-      </c>
-      <c r="AG3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>6.5</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45650.41666666666</v>
